--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-04-2026.xlsx
@@ -533,17 +533,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£13.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£13.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£13.00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£12.58</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>£14.51</t>
+          <t>£14.80</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>£15.41</t>
+          <t>Price Not Found</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>£18.33</t>
+          <t>£18.70</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£32.42</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>£19.04</t>
+          <t>Error: HTTPSConnectionPool(host='www.tradeinsulations.co.uk', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>£23.65</t>
+          <t>Error: ('Connection aborted.', ConnectionAbortedError(10053, 'An established connection was aborted by the software in your host machine'))</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>£26.52</t>
+          <t>£27.05</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>£26.56</t>
+          <t>£27.09</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>£30.14</t>
+          <t>£30.74</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>£33.18</t>
+          <t>£33.84</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£31.77</t>
+          <t>£32.50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£31.77</t>
+          <t>£32.50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£31.77</t>
+          <t>£32.50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>£32.65</t>
+          <t>£33.30</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>£39.68</t>
+          <t>£40.47</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£40.95</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>£47.85</t>
+          <t>£48.81</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>£50.49</t>
+          <t>£51.50</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1821,17 +1821,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£47.76</t>
+          <t>£48.52</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£47.76</t>
+          <t>£48.52</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£47.76</t>
+          <t>£48.52</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>£48.52</t>
+          <t>£49.49</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>£937.8</t>
+          <t>£956.52</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>£1226.4</t>
+          <t>£1250.88</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>£38.02</t>
+          <t>£42.24</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>£33.82</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>£45.21</t>
+          <t>£50.23</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>£41.79</t>
+          <t>£42.63</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>£53.64</t>
+          <t>£59.60</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>£44.48</t>
+          <t>£45.37</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>£58.99</t>
+          <t>£65.54</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>£50.98</t>
+          <t>£52.00</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>£55.00</t>
+          <t>£56.10</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>£52.60</t>
+          <t>£53.65</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>£1,111.12</t>
+          <t>£1,133.34</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>£52.53</t>
+          <t>£53.58</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>£1442.88</t>
+          <t>£1471.68</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>£1606.4</t>
+          <t>£1638.56</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>£1635.2</t>
+          <t>£1667.84</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
